--- a/output/pdf_financials_xlsx/ASHL.xlsx
+++ b/output/pdf_financials_xlsx/ASHL.xlsx
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.661093</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.869436</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.122496</v>
       </c>
     </row>
     <row r="93">
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.6145929999999999</v>
+        <v>0.333278</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.164795</v>
+        <v>0.006776</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.4319</v>
+        <v>-0.069436</v>
       </c>
     </row>
     <row r="119">
@@ -3206,7 +3206,11 @@
           <t>Warrant reserves (Note 7e)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
         <v>0.661093</v>
       </c>
@@ -3744,7 +3748,11 @@
           <t>Exploration and evaluation expenditures (Note 5)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
         <v>-0.281315</v>
       </c>

--- a/output/pdf_financials_xlsx/ASHL.xlsx
+++ b/output/pdf_financials_xlsx/ASHL.xlsx
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.5e-05</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.254324</v>
+        <v>-1.254339</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.754177</v>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.254324</v>
+        <v>-1.254339</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.754177</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.022171</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.017103</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.212612</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.022171</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.017103</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.212612</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.034741</v>
+        <v>0.01257</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.035211</v>
+        <v>0.018108</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.222401</v>
+        <v>0.009789000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">

--- a/output/pdf_financials_xlsx/ASHL.xlsx
+++ b/output/pdf_financials_xlsx/ASHL.xlsx
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>-0.2162</v>
+        <v>-0.236075</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0.099234</v>
+        <v>0.071077</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.054489</v>
       </c>
     </row>
     <row r="102">
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.165001</v>
+        <v>-0.184876</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.098995</v>
+        <v>0.070838</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.023322</v>
+        <v>0.031167</v>
       </c>
     </row>
     <row r="107">
@@ -3537,7 +3537,11 @@
           <t>HST/GST receivable</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>-0.019875</v>
       </c>
